--- a/data/gravel/Chumba Cenote Ti 2025.xlsx
+++ b/data/gravel/Chumba Cenote Ti 2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47FE76AB-F2AC-6848-93B3-2B8DEC1EEF35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18936C20-C413-544A-A2AC-81A3DD591E92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25940" yWindow="-19360" windowWidth="25680" windowHeight="16760" xr2:uid="{ABFFBBBD-2C2A-DA41-8959-3BF392F3D8AC}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{ABFFBBBD-2C2A-DA41-8959-3BF392F3D8AC}"/>
   </bookViews>
   <sheets>
     <sheet name="Chumba Cenote 2025" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="86">
   <si>
     <t>model</t>
   </si>
@@ -291,6 +291,9 @@
   </si>
   <si>
     <t>a10:h33</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 50-80 recommended. I filled this in.</t>
   </si>
 </sst>
 </file>
@@ -3099,6 +3102,27 @@
       <c r="A27" s="1" t="s">
         <v>20</v>
       </c>
+      <c r="C27" s="1">
+        <v>50</v>
+      </c>
+      <c r="D27" s="1">
+        <v>60</v>
+      </c>
+      <c r="E27" s="1">
+        <v>70</v>
+      </c>
+      <c r="F27" s="1">
+        <v>70</v>
+      </c>
+      <c r="G27" s="1">
+        <v>80</v>
+      </c>
+      <c r="H27" s="1">
+        <v>80</v>
+      </c>
+      <c r="I27" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="S27"/>
     </row>
     <row r="28" spans="1:19">

--- a/data/gravel/Chumba Cenote Ti 2025.xlsx
+++ b/data/gravel/Chumba Cenote Ti 2025.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10608"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18936C20-C413-544A-A2AC-81A3DD591E92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F29C322-7A6F-F84D-8783-F41F7E6DE200}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{ABFFBBBD-2C2A-DA41-8959-3BF392F3D8AC}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="27540" windowHeight="13500" xr2:uid="{ABFFBBBD-2C2A-DA41-8959-3BF392F3D8AC}"/>
   </bookViews>
   <sheets>
-    <sheet name="Chumba Cenote 2025" sheetId="1" r:id="rId1"/>
+    <sheet name="Chumba Cenote Ti 2025" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="120">
   <si>
     <t>model</t>
   </si>
@@ -155,12 +155,6 @@
     <t>material</t>
   </si>
   <si>
-    <t>frame weight</t>
-  </si>
-  <si>
-    <t>UDH</t>
-  </si>
-  <si>
     <t>yes</t>
   </si>
   <si>
@@ -170,15 +164,9 @@
     <t>Seat Tube Angle</t>
   </si>
   <si>
-    <t>Trail | mm</t>
-  </si>
-  <si>
     <t>Chumba</t>
   </si>
   <si>
-    <t>Cenote</t>
-  </si>
-  <si>
     <t>https://chumbausa.com/cenote-titanium-suspension-gravel-bike</t>
   </si>
   <si>
@@ -290,17 +278,131 @@
     <t>measure range</t>
   </si>
   <si>
-    <t>a10:h33</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 50-80 recommended. I filled this in.</t>
+  </si>
+  <si>
+    <t>udh</t>
+  </si>
+  <si>
+    <t>dropout</t>
+  </si>
+  <si>
+    <t>650B tire max</t>
+  </si>
+  <si>
+    <t>suspension corrected</t>
+  </si>
+  <si>
+    <t>rear axle</t>
+  </si>
+  <si>
+    <t>front axle</t>
+  </si>
+  <si>
+    <t>q-factor</t>
+  </si>
+  <si>
+    <t>seatpost diameter</t>
+  </si>
+  <si>
+    <t>routing shifter</t>
+  </si>
+  <si>
+    <t>routing dropper</t>
+  </si>
+  <si>
+    <t>chainring 1</t>
+  </si>
+  <si>
+    <t>chainring 2</t>
+  </si>
+  <si>
+    <t>bottom bracket</t>
+  </si>
+  <si>
+    <t>mounts inner</t>
+  </si>
+  <si>
+    <t>mounts under</t>
+  </si>
+  <si>
+    <t>mounts top</t>
+  </si>
+  <si>
+    <t>mounts fork</t>
+  </si>
+  <si>
+    <t>mounts fender rear</t>
+  </si>
+  <si>
+    <t>mounts fender front</t>
+  </si>
+  <si>
+    <t>mounts rack</t>
+  </si>
+  <si>
+    <t>rotor max front</t>
+  </si>
+  <si>
+    <t>rotor max rear</t>
+  </si>
+  <si>
+    <t>frameset</t>
+  </si>
+  <si>
+    <t>currency</t>
+  </si>
+  <si>
+    <t>us</t>
+  </si>
+  <si>
+    <t>external</t>
+  </si>
+  <si>
+    <t>frame_weight</t>
+  </si>
+  <si>
+    <t>front derailleur</t>
+  </si>
+  <si>
+    <t>base build</t>
+  </si>
+  <si>
+    <t>routing dynamo</t>
+  </si>
+  <si>
+    <t>fork suspension</t>
+  </si>
+  <si>
+    <t>stem suspension</t>
+  </si>
+  <si>
+    <t>rear suspension</t>
+  </si>
+  <si>
+    <t>no</t>
+  </si>
+  <si>
+    <t>internal storage</t>
+  </si>
+  <si>
+    <t>Cenote Ti</t>
+  </si>
+  <si>
+    <t>a10:h34</t>
+  </si>
+  <si>
+    <t>700c width max</t>
+  </si>
+  <si>
+    <t>ISO ASTM</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <fonts count="8">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -336,6 +438,18 @@
       <color theme="1"/>
       <name val="Futura Medium"/>
     </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="Futura Medium"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Futura"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -357,7 +471,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -365,6 +479,14 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="15" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -388,13 +510,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>31</xdr:row>
+      <xdr:row>32</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>32</xdr:row>
+      <xdr:row>33</xdr:row>
       <xdr:rowOff>50800</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -436,13 +558,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>29</xdr:row>
+      <xdr:row>30</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>30</xdr:row>
+      <xdr:row>31</xdr:row>
       <xdr:rowOff>50800</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -484,7 +606,7 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>29</xdr:row>
+      <xdr:row>30</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="304800" cy="304800"/>
@@ -527,7 +649,7 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>29</xdr:row>
+      <xdr:row>30</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="304800" cy="304800"/>
@@ -570,7 +692,7 @@
     <xdr:from>
       <xdr:col>8</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>29</xdr:row>
+      <xdr:row>30</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="304800" cy="304800"/>
@@ -613,7 +735,7 @@
     <xdr:from>
       <xdr:col>10</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>29</xdr:row>
+      <xdr:row>30</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="304800" cy="304800"/>
@@ -656,7 +778,7 @@
     <xdr:from>
       <xdr:col>11</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>29</xdr:row>
+      <xdr:row>30</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="304800" cy="304800"/>
@@ -699,7 +821,7 @@
     <xdr:from>
       <xdr:col>11</xdr:col>
       <xdr:colOff>88900</xdr:colOff>
-      <xdr:row>28</xdr:row>
+      <xdr:row>29</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="304800" cy="317500"/>
@@ -742,7 +864,7 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>29</xdr:row>
+      <xdr:row>30</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="304800" cy="317500"/>
@@ -785,7 +907,7 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>29</xdr:row>
+      <xdr:row>30</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="304800" cy="317500"/>
@@ -828,7 +950,7 @@
     <xdr:from>
       <xdr:col>8</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>29</xdr:row>
+      <xdr:row>30</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="304800" cy="317500"/>
@@ -871,7 +993,7 @@
     <xdr:from>
       <xdr:col>10</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>29</xdr:row>
+      <xdr:row>30</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="304800" cy="317500"/>
@@ -914,7 +1036,7 @@
     <xdr:from>
       <xdr:col>11</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>29</xdr:row>
+      <xdr:row>30</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="304800" cy="317500"/>
@@ -957,7 +1079,7 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>12700</xdr:colOff>
-      <xdr:row>28</xdr:row>
+      <xdr:row>29</xdr:row>
       <xdr:rowOff>165100</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="304800" cy="304800"/>
@@ -1000,7 +1122,7 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>29</xdr:row>
+      <xdr:row>30</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="304800" cy="304800"/>
@@ -1043,7 +1165,7 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>29</xdr:row>
+      <xdr:row>30</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="304800" cy="304800"/>
@@ -1086,7 +1208,7 @@
     <xdr:from>
       <xdr:col>8</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>30</xdr:row>
+      <xdr:row>31</xdr:row>
       <xdr:rowOff>50800</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="304800" cy="304800"/>
@@ -1129,7 +1251,7 @@
     <xdr:from>
       <xdr:col>10</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>29</xdr:row>
+      <xdr:row>30</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="304800" cy="304800"/>
@@ -1172,7 +1294,7 @@
     <xdr:from>
       <xdr:col>11</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>29</xdr:row>
+      <xdr:row>30</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="304800" cy="304800"/>
@@ -1215,7 +1337,7 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>29</xdr:row>
+      <xdr:row>30</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="304800" cy="304800"/>
@@ -1258,7 +1380,7 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>29</xdr:row>
+      <xdr:row>30</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="304800" cy="304800"/>
@@ -1301,7 +1423,7 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>29</xdr:row>
+      <xdr:row>30</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="304800" cy="304800"/>
@@ -1344,7 +1466,7 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>29</xdr:row>
+      <xdr:row>30</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="304800" cy="304800"/>
@@ -1387,7 +1509,7 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>29</xdr:row>
+      <xdr:row>30</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="304800" cy="304800"/>
@@ -1430,7 +1552,7 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>29</xdr:row>
+      <xdr:row>30</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="304800" cy="304800"/>
@@ -1473,7 +1595,7 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>29</xdr:row>
+      <xdr:row>30</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="304800" cy="304800"/>
@@ -1516,7 +1638,7 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>29</xdr:row>
+      <xdr:row>30</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="304800" cy="304800"/>
@@ -1602,7 +1724,7 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>29</xdr:row>
+      <xdr:row>30</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="304800" cy="304800"/>
@@ -1645,7 +1767,7 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>29</xdr:row>
+      <xdr:row>30</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="304800" cy="304800"/>
@@ -1688,7 +1810,7 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>29</xdr:row>
+      <xdr:row>30</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="304800" cy="304800"/>
@@ -1731,7 +1853,7 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>29</xdr:row>
+      <xdr:row>30</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="304800" cy="304800"/>
@@ -1774,7 +1896,7 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>29</xdr:row>
+      <xdr:row>30</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="304800" cy="304800"/>
@@ -1817,7 +1939,7 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>29</xdr:row>
+      <xdr:row>30</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="304800" cy="304800"/>
@@ -1860,7 +1982,7 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>29</xdr:row>
+      <xdr:row>30</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="304800" cy="304800"/>
@@ -1903,7 +2025,7 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>29</xdr:row>
+      <xdr:row>30</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="304800" cy="304800"/>
@@ -2262,32 +2384,35 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3856DE37-3828-6849-A98A-EC05E320BDEE}">
-  <dimension ref="A1:AA36"/>
+  <dimension ref="A1:AH37"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="29.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="27.6640625" style="1" customWidth="1"/>
-    <col min="3" max="8" width="13.5" style="1" customWidth="1"/>
-    <col min="9" max="16384" width="10.83203125" style="1"/>
+    <col min="3" max="6" width="13.5" style="1" customWidth="1"/>
+    <col min="7" max="9" width="13.33203125" style="1" customWidth="1"/>
+    <col min="10" max="12" width="10.83203125" style="1"/>
+    <col min="13" max="13" width="13" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27">
+    <row r="1" spans="1:34">
       <c r="A1" s="1" t="s">
         <v>37</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="2" spans="1:27">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="2" spans="1:34">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="3" spans="1:27">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="3" spans="1:34">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -2295,7 +2420,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="4" spans="1:27">
+    <row r="4" spans="1:34">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
@@ -2303,52 +2428,190 @@
         <v>45846</v>
       </c>
     </row>
-    <row r="5" spans="1:27">
+    <row r="5" spans="1:34">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="6" spans="1:27">
-      <c r="A6" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="6" spans="1:34" s="7" customFormat="1" ht="44" customHeight="1">
+      <c r="A6" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="H6" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="I6" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="J6" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="K6" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="L6" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="M6" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="N6" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="O6" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="P6" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="Q6" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="R6" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="S6" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="T6" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="U6" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="V6" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="W6" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="X6" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="Y6" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="Z6" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="AA6" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="AB6" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="AC6" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="AD6" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="AE6" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="AF6" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="AG6" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="AH6" s="8" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="7" spans="1:34">
+      <c r="A7" s="1" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="7" spans="1:27">
-      <c r="A7" s="1" t="s">
+      <c r="B7" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="8" spans="1:27">
-      <c r="A8" s="1" t="s">
+      <c r="C7" s="1">
+        <v>20</v>
+      </c>
+      <c r="D7" s="1">
+        <v>50</v>
+      </c>
+      <c r="F7" s="1">
         <v>40</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="9" spans="1:27">
+      <c r="G7" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="J7" s="1">
+        <v>142</v>
+      </c>
+      <c r="K7" s="1">
+        <v>100</v>
+      </c>
+      <c r="N7" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="O7" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="P7" s="9"/>
+      <c r="Q7" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="R7" s="1">
+        <v>44</v>
+      </c>
+      <c r="AE7" s="1">
+        <v>1695</v>
+      </c>
+      <c r="AF7" s="7"/>
+      <c r="AG7" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="AH7" s="1" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="8" spans="1:34">
+      <c r="M8" s="6"/>
+    </row>
+    <row r="9" spans="1:34">
       <c r="A9" s="1" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="10" spans="1:27">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="10" spans="1:34">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C10" s="1">
         <v>50</v>
@@ -2369,7 +2632,7 @@
         <v>60</v>
       </c>
       <c r="J10" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="K10" s="1">
         <v>50</v>
@@ -2417,12 +2680,12 @@
         <v>36</v>
       </c>
     </row>
-    <row r="11" spans="1:27">
+    <row r="11" spans="1:34">
       <c r="A11" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C11" s="1">
         <v>524</v>
@@ -2443,25 +2706,25 @@
         <v>618</v>
       </c>
       <c r="J11" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="L11" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="M11" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="N11" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="K11" s="1" t="s">
+      <c r="O11" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="L11" s="1" t="s">
+      <c r="P11" s="1" t="s">
         <v>52</v>
-      </c>
-      <c r="M11" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="N11" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="O11" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="P11" s="1" t="s">
-        <v>56</v>
       </c>
       <c r="S11" s="4"/>
       <c r="T11" s="4"/>
@@ -2473,12 +2736,12 @@
       <c r="Z11" s="4"/>
       <c r="AA11" s="4"/>
     </row>
-    <row r="12" spans="1:27">
+    <row r="12" spans="1:34">
       <c r="A12" s="1" t="s">
         <v>10</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C12" s="1">
         <v>70</v>
@@ -2499,7 +2762,7 @@
         <v>70</v>
       </c>
       <c r="J12" s="6" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="K12" s="1">
         <v>524</v>
@@ -2529,12 +2792,12 @@
       <c r="Z12" s="3"/>
       <c r="AA12" s="3"/>
     </row>
-    <row r="13" spans="1:27">
+    <row r="13" spans="1:34">
       <c r="A13" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C13" s="1">
         <v>90</v>
@@ -2555,25 +2818,25 @@
         <v>180</v>
       </c>
       <c r="J13" s="6" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="O13" s="1" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="P13" s="1" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="S13" s="3"/>
       <c r="T13" s="3"/>
@@ -2585,12 +2848,12 @@
       <c r="Z13" s="3"/>
       <c r="AA13" s="3"/>
     </row>
-    <row r="14" spans="1:27">
+    <row r="14" spans="1:34">
       <c r="A14" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C14" s="1">
         <v>74.5</v>
@@ -2611,7 +2874,7 @@
         <v>73.5</v>
       </c>
       <c r="J14" s="6" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="K14" s="1">
         <v>90</v>
@@ -2641,12 +2904,12 @@
       <c r="Z14" s="3"/>
       <c r="AA14" s="3"/>
     </row>
-    <row r="15" spans="1:27">
+    <row r="15" spans="1:34">
       <c r="A15" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C15" s="1">
         <v>430</v>
@@ -2667,25 +2930,25 @@
         <v>545</v>
       </c>
       <c r="J15" s="6" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="O15" s="1" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="P15" s="1" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="S15" s="3"/>
       <c r="T15" s="3"/>
@@ -2697,19 +2960,19 @@
       <c r="Z15" s="3"/>
       <c r="AA15" s="3"/>
     </row>
-    <row r="16" spans="1:27">
+    <row r="16" spans="1:34">
       <c r="A16" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="C16" s="1">
         <f>VALUE(LEFT(K17,3))</f>
         <v>425</v>
       </c>
       <c r="D16" s="1">
-        <f t="shared" ref="D16:H16" si="0">VALUE(LEFT(L17,3))</f>
+        <f t="shared" ref="D16:F16" si="0">VALUE(LEFT(L17,3))</f>
         <v>425</v>
       </c>
       <c r="E16" s="1">
@@ -2721,15 +2984,15 @@
         <v>425</v>
       </c>
       <c r="G16" s="1">
-        <f t="shared" si="0"/>
+        <f>VALUE(LEFT(O17,3))</f>
         <v>425</v>
       </c>
       <c r="H16" s="1">
-        <f t="shared" si="0"/>
+        <f>VALUE(LEFT(P17,3))</f>
         <v>430</v>
       </c>
       <c r="J16" s="6" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="K16" s="1">
         <v>430</v>
@@ -2764,7 +3027,7 @@
         <v>15</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C17" s="1">
         <v>68</v>
@@ -2785,25 +3048,25 @@
         <v>65</v>
       </c>
       <c r="J17" s="6" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="M17" s="1" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="O17" s="1" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="P17" s="1" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="18" spans="1:19">
@@ -2811,14 +3074,14 @@
         <v>14</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="C18" s="1">
         <f>VALUE(LEFT(K19,4))</f>
         <v>1015</v>
       </c>
       <c r="D18" s="1">
-        <f t="shared" ref="D18:H18" si="1">VALUE(LEFT(L19,4))</f>
+        <f t="shared" ref="D18:F18" si="1">VALUE(LEFT(L19,4))</f>
         <v>1028</v>
       </c>
       <c r="E18" s="1">
@@ -2830,15 +3093,15 @@
         <v>1067</v>
       </c>
       <c r="G18" s="1">
-        <f t="shared" si="1"/>
+        <f>VALUE(LEFT(O19,4))</f>
         <v>1084</v>
       </c>
       <c r="H18" s="1">
-        <f t="shared" si="1"/>
+        <f>VALUE(LEFT(P19,4))</f>
         <v>1111</v>
       </c>
       <c r="J18" s="6" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="K18" s="1">
         <v>68</v>
@@ -2864,7 +3127,7 @@
         <v>22</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C19" s="1">
         <f>VALUE(LEFT(K20,4))*25.4</f>
@@ -2891,25 +3154,25 @@
         <v>830.58</v>
       </c>
       <c r="J19" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="K19" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="L19" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="M19" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="N19" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="K19" s="1" t="s">
+      <c r="O19" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="L19" s="1" t="s">
+      <c r="P19" s="1" t="s">
         <v>70</v>
-      </c>
-      <c r="M19" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="N19" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="O19" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="P19" s="1" t="s">
-        <v>74</v>
       </c>
       <c r="S19"/>
     </row>
@@ -2918,7 +3181,7 @@
         <v>7</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C20" s="1">
         <v>370</v>
@@ -2939,25 +3202,25 @@
         <v>430</v>
       </c>
       <c r="J20" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="K20" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="L20" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="M20" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="N20" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="O20" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="K20" s="1" t="s">
+      <c r="P20" s="1" t="s">
         <v>76</v>
-      </c>
-      <c r="L20" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="M20" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="N20" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="O20" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="P20" s="1" t="s">
-        <v>80</v>
       </c>
       <c r="S20"/>
     </row>
@@ -2966,7 +3229,7 @@
         <v>8</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C21" s="1">
         <v>555</v>
@@ -2987,7 +3250,7 @@
         <v>637</v>
       </c>
       <c r="J21" s="6" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="K21" s="1">
         <v>370</v>
@@ -3033,7 +3296,7 @@
         <v>45</v>
       </c>
       <c r="J22" s="6" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="K22" s="1">
         <v>555</v>
@@ -3094,94 +3357,76 @@
     </row>
     <row r="26" spans="1:19">
       <c r="A26" s="1" t="s">
-        <v>19</v>
+        <v>107</v>
       </c>
       <c r="S26"/>
     </row>
     <row r="27" spans="1:19">
       <c r="A27" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C27" s="1">
-        <v>50</v>
-      </c>
-      <c r="D27" s="1">
-        <v>60</v>
-      </c>
-      <c r="E27" s="1">
-        <v>70</v>
-      </c>
-      <c r="F27" s="1">
-        <v>70</v>
-      </c>
-      <c r="G27" s="1">
-        <v>80</v>
-      </c>
-      <c r="H27" s="1">
-        <v>80</v>
-      </c>
-      <c r="I27" s="1" t="s">
-        <v>85</v>
+        <v>19</v>
       </c>
       <c r="S27"/>
     </row>
     <row r="28" spans="1:19">
       <c r="A28" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
+      </c>
+      <c r="C28" s="1">
+        <v>50</v>
+      </c>
+      <c r="D28" s="1">
+        <v>60</v>
+      </c>
+      <c r="E28" s="1">
+        <v>70</v>
+      </c>
+      <c r="F28" s="1">
+        <v>70</v>
+      </c>
+      <c r="G28" s="1">
+        <v>80</v>
+      </c>
+      <c r="H28" s="1">
+        <v>80</v>
+      </c>
+      <c r="I28" s="1" t="s">
+        <v>80</v>
       </c>
       <c r="S28"/>
     </row>
     <row r="29" spans="1:19">
       <c r="A29" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C29" s="1">
-        <v>700</v>
-      </c>
-      <c r="D29" s="1">
-        <v>700</v>
-      </c>
-      <c r="E29" s="1">
-        <v>700</v>
-      </c>
-      <c r="F29" s="1">
-        <v>700</v>
-      </c>
-      <c r="G29" s="1">
-        <v>700</v>
-      </c>
-      <c r="H29" s="1">
-        <v>700</v>
+        <v>21</v>
       </c>
       <c r="S29"/>
     </row>
     <row r="30" spans="1:19">
       <c r="A30" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C30" s="1">
-        <v>50</v>
+        <v>700</v>
       </c>
       <c r="D30" s="1">
-        <v>50</v>
+        <v>700</v>
       </c>
       <c r="E30" s="1">
-        <v>50</v>
+        <v>700</v>
       </c>
       <c r="F30" s="1">
-        <v>50</v>
+        <v>700</v>
       </c>
       <c r="G30" s="1">
-        <v>50</v>
+        <v>700</v>
       </c>
       <c r="H30" s="1">
-        <v>50</v>
+        <v>700</v>
       </c>
       <c r="S30"/>
     </row>
     <row r="31" spans="1:19">
       <c r="A31" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C31" s="1">
         <v>50</v>
@@ -3205,111 +3450,135 @@
     </row>
     <row r="32" spans="1:19">
       <c r="A32" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C32" s="1">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="D32" s="1">
-        <v>160</v>
+        <v>50</v>
       </c>
       <c r="E32" s="1">
-        <v>168</v>
+        <v>50</v>
       </c>
       <c r="F32" s="1">
-        <v>176</v>
+        <v>50</v>
       </c>
       <c r="G32" s="1">
-        <v>184</v>
+        <v>50</v>
       </c>
       <c r="H32" s="1">
-        <v>192</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="S32"/>
     </row>
     <row r="33" spans="1:8">
       <c r="A33" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C33" s="1">
+        <v>150</v>
+      </c>
+      <c r="D33" s="1">
+        <v>160</v>
+      </c>
+      <c r="E33" s="1">
+        <v>168</v>
+      </c>
+      <c r="F33" s="1">
+        <v>176</v>
+      </c>
+      <c r="G33" s="1">
+        <v>184</v>
+      </c>
+      <c r="H33" s="1">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8">
+      <c r="A34" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C33" s="1">
+      <c r="C34" s="1">
         <v>160</v>
       </c>
-      <c r="D33" s="1">
+      <c r="D34" s="1">
         <v>168</v>
       </c>
-      <c r="E33" s="1">
+      <c r="E34" s="1">
         <v>176</v>
       </c>
-      <c r="F33" s="1">
+      <c r="F34" s="1">
         <v>184</v>
       </c>
-      <c r="G33" s="1">
+      <c r="G34" s="1">
         <v>192</v>
       </c>
-      <c r="H33" s="1">
+      <c r="H34" s="1">
         <v>200</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8">
-      <c r="C34" s="1">
-        <v>60</v>
-      </c>
-      <c r="D34" s="1">
-        <v>63.5</v>
-      </c>
-      <c r="E34" s="1">
-        <v>67.5</v>
-      </c>
-      <c r="F34" s="1">
-        <v>70</v>
-      </c>
-      <c r="G34" s="1">
-        <v>72</v>
-      </c>
-      <c r="H34" s="1">
-        <v>73.5</v>
       </c>
     </row>
     <row r="35" spans="1:8">
       <c r="C35" s="1">
+        <v>60</v>
+      </c>
+      <c r="D35" s="1">
         <v>63.5</v>
       </c>
-      <c r="D35" s="1">
+      <c r="E35" s="1">
         <v>67.5</v>
       </c>
-      <c r="E35" s="1">
+      <c r="F35" s="1">
         <v>70</v>
       </c>
-      <c r="F35" s="1">
+      <c r="G35" s="1">
         <v>72</v>
       </c>
-      <c r="G35" s="1">
+      <c r="H35" s="1">
         <v>73.5</v>
       </c>
-      <c r="H35" s="1">
+    </row>
+    <row r="36" spans="1:8">
+      <c r="C36" s="1">
+        <v>63.5</v>
+      </c>
+      <c r="D36" s="1">
+        <v>67.5</v>
+      </c>
+      <c r="E36" s="1">
+        <v>70</v>
+      </c>
+      <c r="F36" s="1">
+        <v>72</v>
+      </c>
+      <c r="G36" s="1">
+        <v>73.5</v>
+      </c>
+      <c r="H36" s="1">
         <v>75</v>
       </c>
     </row>
-    <row r="36" spans="1:8">
-      <c r="B36" s="6" t="s">
+    <row r="37" spans="1:8">
+      <c r="B37" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="F37" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C36" s="1" t="s">
+      <c r="G37" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D36" s="1" t="s">
+      <c r="H37" s="1" t="s">
         <v>52</v>
-      </c>
-      <c r="E36" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="F36" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="G36" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="H36" s="1" t="s">
-        <v>56</v>
       </c>
     </row>
   </sheetData>
